--- a/raw-data/VFT demog sites GPS coords.xlsx
+++ b/raw-data/VFT demog sites GPS coords.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\VFT\VFT_github\zyao78VFTcode\raw-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC7DAAB0-B750-49C8-B2B7-EFACD6611663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{486A52A2-803C-4542-9084-A780D15DF237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="33517" yWindow="3818" windowWidth="2356" windowHeight="532" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Croatan" sheetId="1" r:id="rId1"/>

--- a/raw-data/VFT demog sites GPS coords.xlsx
+++ b/raw-data/VFT demog sites GPS coords.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\VFT\VFT_github\zyao78VFTcode\raw-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{486A52A2-803C-4542-9084-A780D15DF237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{931F0DF5-75C5-4280-99C2-23BCBF8F66EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="45960" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Croatan" sheetId="1" r:id="rId1"/>
